--- a/analisis_partidos_full.xlsx
+++ b/analisis_partidos_full.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA2"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,458 +429,1376 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>H2H_1</t>
+          <t>Prob_BTTS</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>H2H_2</t>
+          <t>Prob_Over2.5</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>H2H_3</t>
+          <t>Prob_Under2.5</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>H2H_4</t>
+          <t>Value_BTTS</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>H2H_5</t>
+          <t>Value_Over2.5</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Local_1</t>
+          <t>Value_Under2.5</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Local_2</t>
+          <t>Pick</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Local_3</t>
+          <t>Confianza</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Local_4</t>
+          <t>Ganador</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Local_5</t>
+          <t>Handicap</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Visitante_1</t>
+          <t>Cuota</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Visitante_2</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Visitante_3</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Visitante_4</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Visitante_5</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>H2H_Promedio</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>H2H_BTTS</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>H2H_Over2.5</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>H2H_Under2.5</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>H2H_CS_Local</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>H2H_CS_Visitante</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Local_Promedio</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Local_BTTS</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Local_Over2.5</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Local_Under2.5</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Local_CS_Local</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Local_CS_Visitante</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Visitante_Promedio</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Visitante_BTTS</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Visitante_Over2.5</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Visitante_Under2.5</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Visitante_CS_Local</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Visitante_CS_Visitante</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Prob_BTTS</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Prob_Over2.5</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>Prob_Under2.5</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Prob_CS_Local</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Prob_CS_Visitante</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>Value_BTTS</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>Value_Over2.5</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>Fuerza_Partido</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Diff_BTTS</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Pick</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>Confianza</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>Escenario_Probable</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>BTTS_Fuerte</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>Under_Fuerte</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>Value_Bet</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>Partido_Trampa</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>CleanSheet_Local_Fuerte</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>CleanSheet_Visitante_Fuerte</t>
+          <t>Resultado</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Aguilas Doradas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-47.85</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-71.14</v>
+      </c>
+      <c r="H2" t="n">
+        <v>18.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>3-3</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>4-1</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>3-0</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S2" t="n">
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Llaneros</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Alianza</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-48.71</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BTTS</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Inter Bogotá</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-73.23</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-44.62</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>47</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-53.8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-35.26</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D6" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>53</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-46.96</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>40</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>65</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-50.08</v>
+      </c>
+      <c r="H7" t="n">
+        <v>17</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>34</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-13.38</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-38.8</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Estrasburgo</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>47</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-20.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-32.33</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-58.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-65.68000000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>17</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-40.68</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-40.6</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Stade Rennais</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>22</v>
+      </c>
+      <c r="D12" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>41</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-61.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-51.06</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-26.2</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Marsella</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Niza</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>53</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-63.07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-48.13</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>54</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-54.33</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-52.23</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>59</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-51.52</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-39.16</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>46</v>
+      </c>
+      <c r="E16" t="n">
+        <v>34</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-44.35</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-38.8</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Friburgo</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-44.35</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-26.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-26.2</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Gimnasia Mendoza</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>73</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-39.62</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-79.33</v>
+      </c>
+      <c r="H18" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Belgrano</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gimnasia L.P.</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>51</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-57.48</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-37.41</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Atl. Tucumán</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>59</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-45.4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-53.59</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Waregem</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RAAL La Louviere</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>28</v>
+      </c>
+      <c r="E21" t="n">
+        <v>53</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-47.85</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-45.4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Gent</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Club Brujas</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>40</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-16.73</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KV Mechelen</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>St. Truiden</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>54</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-46.63</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-56.52</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Anderlecht</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Royale Union SG</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>72</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-60.62</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-74.26000000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Real Sporting</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>60</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-30.53</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-54.56</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>48</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-7.07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-21.02</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mirandés</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cultural Leonesa</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>73</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-73.09</v>
+      </c>
+      <c r="H27" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Real Zaragoza</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>60</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-7.07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-62.17</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Leganés</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Andorra</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>53</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-7.07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-30.78</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AD Ceuta</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>R. Racing Club</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="D30" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="E30" t="n">
         <v>20</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>100</v>
-      </c>
-      <c r="V2" t="n">
-        <v>80</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-11.56</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-12.63</v>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Cerrado</t>
-        </is>
-      </c>
-      <c r="AR2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="b">
-        <v>0</v>
-      </c>
+      <c r="F30" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="G30" t="n">
+        <v>82.52</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-64</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NO CLARO</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/analisis_partidos_full.xlsx
+++ b/analisis_partidos_full.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,40 +491,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29.8</v>
+        <v>33.8</v>
       </c>
       <c r="D2" t="n">
-        <v>14.8</v>
+        <v>43.8</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>-47.85</v>
+        <v>-40.85</v>
       </c>
       <c r="G2" t="n">
-        <v>-71.14</v>
+        <v>-14.59</v>
       </c>
       <c r="H2" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
-        </is>
-      </c>
+        <v>-28</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -539,40 +535,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Llaneros</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alianza</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>60.8</v>
+        <v>37.7</v>
       </c>
       <c r="D3" t="n">
-        <v>26.3</v>
+        <v>21.2</v>
       </c>
       <c r="E3" t="n">
         <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>6.4</v>
+        <v>-34.02</v>
       </c>
       <c r="G3" t="n">
-        <v>-48.71</v>
+        <v>-58.66</v>
       </c>
       <c r="H3" t="n">
         <v>8</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>BTTS</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -587,31 +579,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Inter Bogotá</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boyacá Chicó</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15.3</v>
+        <v>19.2</v>
       </c>
       <c r="D4" t="n">
-        <v>28.4</v>
+        <v>34.1</v>
       </c>
       <c r="E4" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>-73.23</v>
+        <v>-66.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-44.62</v>
+        <v>-33.5</v>
       </c>
       <c r="H4" t="n">
-        <v>6.2</v>
+        <v>-17.2</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
@@ -631,35 +623,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26.4</v>
+        <v>62.2</v>
       </c>
       <c r="D5" t="n">
-        <v>33.2</v>
+        <v>41.6</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>-53.8</v>
+        <v>8.85</v>
       </c>
       <c r="G5" t="n">
-        <v>-35.26</v>
+        <v>-18.88</v>
       </c>
       <c r="H5" t="n">
-        <v>-15.4</v>
+        <v>-6.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>BTTS</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -679,31 +671,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>22.8</v>
       </c>
       <c r="D6" t="n">
-        <v>27.2</v>
+        <v>11.5</v>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F6" t="n">
-        <v>-30</v>
+        <v>-60.1</v>
       </c>
       <c r="G6" t="n">
-        <v>-46.96</v>
+        <v>-77.56999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.6</v>
+        <v>31.4</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
@@ -723,36 +715,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>40</v>
       </c>
       <c r="D7" t="n">
-        <v>25.6</v>
+        <v>55.8</v>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
         <v>-30</v>
       </c>
       <c r="G7" t="n">
-        <v>-50.08</v>
+        <v>8.81</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>-29.8</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>OVER 2.5</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>BAJA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -767,31 +763,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Qingdao West Coast</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="D8" t="n">
-        <v>57.2</v>
+        <v>19.5</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>-13.38</v>
+        <v>-15.12</v>
       </c>
       <c r="G8" t="n">
-        <v>11.54</v>
+        <v>-61.98</v>
       </c>
       <c r="H8" t="n">
-        <v>-38.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
@@ -811,31 +807,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Henan Songshan Longmen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Estrasburgo</t>
+          <t>Zhejiang Professional</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>45.6</v>
+        <v>27.2</v>
       </c>
       <c r="D9" t="n">
-        <v>34.7</v>
+        <v>53.2</v>
       </c>
       <c r="E9" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>-20.2</v>
+        <v>-52.4</v>
       </c>
       <c r="G9" t="n">
-        <v>-32.33</v>
+        <v>3.74</v>
       </c>
       <c r="H9" t="n">
-        <v>-15.4</v>
+        <v>-49.6</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
@@ -855,35 +851,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Shandong Taishan</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.6</v>
+        <v>35.6</v>
       </c>
       <c r="D10" t="n">
-        <v>17.6</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>-58.7</v>
+        <v>-37.7</v>
       </c>
       <c r="G10" t="n">
-        <v>-65.68000000000001</v>
+        <v>58.73</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>-64</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>UNDER 2.5</t>
+          <t>OVER 2.5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -903,35 +899,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Chongqing Tonglianglong</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="D11" t="n">
-        <v>63.5</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>-40.68</v>
+        <v>-40.85</v>
       </c>
       <c r="G11" t="n">
-        <v>23.83</v>
+        <v>-72.89</v>
       </c>
       <c r="H11" t="n">
-        <v>-40.6</v>
+        <v>26</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>OVER 2.5</t>
+          <t>UNDER 2.5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -951,31 +947,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stade Rennais</t>
+          <t>Shenzhen Xinpengcheng</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>51.3</v>
       </c>
       <c r="D12" t="n">
-        <v>25.1</v>
+        <v>38.8</v>
       </c>
       <c r="E12" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>-61.5</v>
+        <v>-10.22</v>
       </c>
       <c r="G12" t="n">
-        <v>-51.06</v>
+        <v>-24.34</v>
       </c>
       <c r="H12" t="n">
-        <v>-26.2</v>
+        <v>-4.6</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
@@ -995,28 +991,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marsella</t>
+          <t>AD Ceuta</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Niza</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.1</v>
+        <v>30.2</v>
       </c>
       <c r="D13" t="n">
-        <v>26.6</v>
+        <v>24.2</v>
       </c>
       <c r="E13" t="n">
         <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>-63.07</v>
+        <v>-47.15</v>
       </c>
       <c r="G13" t="n">
-        <v>-48.13</v>
+        <v>-52.81</v>
       </c>
       <c r="H13" t="n">
         <v>-4.6</v>
@@ -1039,31 +1035,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Real Sporting</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26.1</v>
+        <v>53.9</v>
       </c>
       <c r="D14" t="n">
-        <v>24.5</v>
+        <v>57.2</v>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
-        <v>-54.33</v>
+        <v>-5.67</v>
       </c>
       <c r="G14" t="n">
-        <v>-52.23</v>
+        <v>11.54</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.8</v>
+        <v>-28</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
@@ -1083,31 +1079,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Os Belenenses</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.7</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>31.2</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F15" t="n">
-        <v>-51.52</v>
+        <v>-54.5</v>
       </c>
       <c r="G15" t="n">
-        <v>-39.16</v>
+        <v>-66.84999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>6.2</v>
+        <v>18.8</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
@@ -1123,682 +1119,6 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D16" t="n">
-        <v>46</v>
-      </c>
-      <c r="E16" t="n">
-        <v>34</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-44.35</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-38.8</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>OVER 2.5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Borussia Dortmund</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Friburgo</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D17" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="E17" t="n">
-        <v>41</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-44.35</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-26.1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-26.2</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Independiente Rivadavia</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Gimnasia Mendoza</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="E18" t="n">
-        <v>73</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-39.62</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-79.33</v>
-      </c>
-      <c r="H18" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Belgrano</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Gimnasia L.P.</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="D19" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>51</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-57.48</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-37.41</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Atl. Tucumán</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Banfield</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E20" t="n">
-        <v>59</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-45.4</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-53.59</v>
-      </c>
-      <c r="H20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>OVER 2.5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Waregem</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>RAAL La Louviere</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="D21" t="n">
-        <v>28</v>
-      </c>
-      <c r="E21" t="n">
-        <v>53</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-47.85</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-45.4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Gent</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Club Brujas</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="D22" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="E22" t="n">
-        <v>40</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-16.73</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-28</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>KV Mechelen</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>St. Truiden</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="E23" t="n">
-        <v>54</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-46.63</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-56.52</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Anderlecht</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Royale Union SG</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="D24" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>72</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-60.62</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-74.26000000000001</v>
-      </c>
-      <c r="H24" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Real Sporting</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="D25" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E25" t="n">
-        <v>60</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-30.53</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-54.56</v>
-      </c>
-      <c r="H25" t="n">
-        <v>8</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Almería</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="E26" t="n">
-        <v>48</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-7.07</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-21.02</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-13.6</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Mirandés</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Cultural Leonesa</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="D27" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="E27" t="n">
-        <v>73</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-17.4</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-73.09</v>
-      </c>
-      <c r="H27" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Huesca</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Real Zaragoza</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="E28" t="n">
-        <v>60</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-7.07</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-62.17</v>
-      </c>
-      <c r="H28" t="n">
-        <v>8</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Leganés</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Andorra</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="E29" t="n">
-        <v>53</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-7.07</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-30.78</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AD Ceuta</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>R. Racing Club</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="D30" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="E30" t="n">
-        <v>20</v>
-      </c>
-      <c r="F30" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="G30" t="n">
-        <v>82.52</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-64</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/analisis_partidos_full.xlsx
+++ b/analisis_partidos_full.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,36 +491,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>México</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>33.8</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>43.8</v>
+        <v>13.8</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>-40.85</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>-14.59</v>
+        <v>-73.09</v>
       </c>
       <c r="H2" t="n">
-        <v>-28</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>UNDER 2.5</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>BAJA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -535,31 +539,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Corea del Sur</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>República Checa</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37.7</v>
+        <v>5.2</v>
       </c>
       <c r="D3" t="n">
-        <v>21.2</v>
+        <v>30.7</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>-34.02</v>
+        <v>-90.64</v>
       </c>
       <c r="G3" t="n">
-        <v>-58.66</v>
+        <v>-40.13</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>-10</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
@@ -579,31 +583,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Zanzíbar</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.2</v>
+        <v>33.4</v>
       </c>
       <c r="D4" t="n">
-        <v>34.1</v>
+        <v>50.2</v>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
-        <v>-66.40000000000001</v>
+        <v>-39.88</v>
       </c>
       <c r="G4" t="n">
-        <v>-33.5</v>
+        <v>-2.11</v>
       </c>
       <c r="H4" t="n">
-        <v>-17.2</v>
+        <v>-49.6</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
@@ -619,506 +623,6 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Botafogo</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>52</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-18.88</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>BTTS</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Grêmio</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Corinthians</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>73</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-60.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-77.56999999999999</v>
-      </c>
-      <c r="H6" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Vitória</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>40</v>
-      </c>
-      <c r="D7" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>39</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8.81</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-29.8</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>OVER 2.5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Qingdao West Coast</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Shanghai Shenhua</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>61</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-15.12</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-61.98</v>
-      </c>
-      <c r="H8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Henan Songshan Longmen</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Zhejiang Professional</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="D9" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>28</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-52.4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-49.6</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Chengdu Rongcheng</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Shandong Taishan</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="D10" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="E10" t="n">
-        <v>20</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-37.7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>58.73</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-64</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>OVER 2.5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Chongqing Tonglianglong</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Beijing Guoan</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="D11" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>70</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-40.85</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-72.89</v>
-      </c>
-      <c r="H11" t="n">
-        <v>26</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>UNDER 2.5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Shenzhen Xinpengcheng</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Qingdao Hainiu</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="E12" t="n">
-        <v>53</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-10.22</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-24.34</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AD Ceuta</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Albacete</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>53</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-47.15</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-52.81</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Real Sporting</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>40</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-5.67</v>
-      </c>
-      <c r="G14" t="n">
-        <v>11.54</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-28</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Os Belenenses</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Farense</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>26</v>
-      </c>
-      <c r="D15" t="n">
-        <v>17</v>
-      </c>
-      <c r="E15" t="n">
-        <v>66</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-54.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-66.84999999999999</v>
-      </c>
-      <c r="H15" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>BAJA</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>NO CLARO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
